--- a/server/resource/excel/template_product_require.xlsx
+++ b/server/resource/excel/template_product_require.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xujun/gva/gin-vue-admin/server/resource/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ted/Projects/gin-vue-admin/server/resource/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F57957B-03EC-DB47-B03A-7828657F861A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969B4B35-0CE1-E448-A641-BD08814BF0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6080" yWindow="2120" windowWidth="20660" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
       <t xml:space="preserve">        S&amp;L FOOD TRADING LTD
@@ -93,6 +93,10 @@
   <si>
     <t>QTY</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GROSS WEIGHT</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -330,14 +334,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="184" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -680,9 +684,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -720,7 +724,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -826,7 +830,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -968,7 +972,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -976,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="52.33203125" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="3" customWidth="1"/>
@@ -986,22 +990,22 @@
     <col min="7" max="7" width="19" style="4" customWidth="1"/>
     <col min="8" max="8" width="14.1640625" style="2" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.1640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="52.33203125" style="1"/>
+    <col min="10" max="11" width="16" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="52.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="62.25" customHeight="1">
-      <c r="B1" s="23" t="s">
+    <row r="1" spans="1:12" ht="62.25" customHeight="1">
+      <c r="B1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23"/>
+      <c r="C1" s="25"/>
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
     </row>
-    <row r="2" spans="1:11" ht="16" customHeight="1"/>
-    <row r="3" spans="1:11" ht="30" customHeight="1">
+    <row r="2" spans="1:12" ht="16" customHeight="1"/>
+    <row r="3" spans="1:12" ht="30" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -1033,14 +1037,17 @@
         <v>8</v>
       </c>
       <c r="K3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1">
+    <row r="4" spans="1:12" ht="30" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="14"/>
-      <c r="D4" s="24"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="14"/>
       <c r="F4" s="9"/>
       <c r="G4" s="10"/>
@@ -1048,12 +1055,13 @@
       <c r="I4" s="20"/>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
     </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1">
+    <row r="5" spans="1:12" ht="30" customHeight="1">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="15"/>
-      <c r="D5" s="25"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="15"/>
       <c r="F5" s="12"/>
       <c r="G5" s="13"/>
@@ -1061,6 +1069,7 @@
       <c r="I5" s="21"/>
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
